--- a/fhir/finnish-smart/StructureDefinition-fi-smart-server-profile.xlsx
+++ b/fhir/finnish-smart/StructureDefinition-fi-smart-server-profile.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0-rc2</t>
+    <t>2.0.0-rc3</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-11T17:07:13+03:00</t>
+    <t>2025-06-01T15:36:45+03:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/finnish-smart/StructureDefinition-fi-smart-server-profile.xlsx
+++ b/fhir/finnish-smart/StructureDefinition-fi-smart-server-profile.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0-rc3</t>
+    <t>2.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-01T15:36:45+03:00</t>
+    <t>2025-10-26T13:24:16+02:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -361,7 +361,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -726,7 +726,7 @@
     <t>Countries and regions within which this artifact is targeted for use.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/jurisdiction</t>
+    <t>http://hl7.org/fhir/ValueSet/jurisdiction|4.0.1</t>
   </si>
   <si>
     <t>Definition.jurisdiction</t>
@@ -797,7 +797,7 @@
     <t>CapabilityStatement.instantiates</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(CapabilityStatement)
+    <t xml:space="preserve">canonical(CapabilityStatement|4.0.1)
 </t>
   </si>
   <si>
@@ -952,7 +952,7 @@
     <t>CapabilityStatement.implementation.custodian</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -1065,7 +1065,7 @@
     <t>CapabilityStatement.implementationGuide</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(ImplementationGuide)
+    <t xml:space="preserve">canonical(ImplementationGuide|4.0.1)
 </t>
   </si>
   <si>
@@ -1176,7 +1176,7 @@
     <t>Types of security services used with FHIR.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/restful-security-service</t>
+    <t>http://hl7.org/fhir/ValueSet/restful-security-service|4.0.1</t>
   </si>
   <si>
     <t>CapabilityStatement.rest.security.description</t>
@@ -1231,7 +1231,7 @@
     <t>CapabilityStatement.rest.resource.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition)
+    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -1481,7 +1481,7 @@
     <t>CapabilityStatement.rest.resource.searchParam.definition</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(SearchParameter)
+    <t xml:space="preserve">canonical(SearchParameter|4.0.1)
 </t>
   </si>
   <si>
@@ -1558,7 +1558,7 @@
     <t>CapabilityStatement.rest.resource.operation.definition</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(OperationDefinition)
+    <t xml:space="preserve">canonical(OperationDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -1643,7 +1643,7 @@
     <t>CapabilityStatement.rest.compartment</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(CompartmentDefinition)
+    <t xml:space="preserve">canonical(CompartmentDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -1715,7 +1715,7 @@
     <t>The protocol used for message transport.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/message-transport</t>
+    <t>http://hl7.org/fhir/ValueSet/message-transport|4.0.1</t>
   </si>
   <si>
     <t>CapabilityStatement.messaging.endpoint.address</t>
@@ -1791,7 +1791,7 @@
     <t>CapabilityStatement.messaging.supportedMessage.definition</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(MessageDefinition)
+    <t xml:space="preserve">canonical(MessageDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -2167,7 +2167,7 @@
     <col min="8" max="8" width="12.6875" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="10.51171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="27.26953125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="31.859375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
